--- a/examples/Templates/Excel/Proceso.xlsx
+++ b/examples/Templates/Excel/Proceso.xlsx
@@ -11,50 +11,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Proceso</t>
   </si>
   <si>
-    <t>{{proceso.file.name}}</t>
-  </si>
-  <si>
     <t>Equipo</t>
   </si>
   <si>
-    <t>{{proceso.team}}</t>
-  </si>
-  <si>
     <t>Rol</t>
   </si>
   <si>
-    <t>{{proceso.role}}</t>
-  </si>
-  <si>
     <t>Seniority</t>
   </si>
   <si>
-    <t>{{proceso.seniority}}</t>
-  </si>
-  <si>
     <t>Vacantes</t>
   </si>
   <si>
-    <t>{{proceso.quantity}}</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
-    <t>{{proceso.status}}</t>
-  </si>
-  <si>
     <t>Contratados</t>
   </si>
   <si>
-    <t>{{hires | count}}</t>
-  </si>
-  <si>
     <t>Candidato</t>
   </si>
   <si>
@@ -76,37 +55,7 @@
     <t>Decisión</t>
   </si>
   <si>
-    <t>{{#each interviews}}{{interviews.interviewed}}</t>
-  </si>
-  <si>
-    <t>{{interviews.interviewed.seniority}}</t>
-  </si>
-  <si>
-    <t>{{interviews.interviewed.stack}}</t>
-  </si>
-  <si>
-    <t>{{interviews.interviewed.linkedin}}</t>
-  </si>
-  <si>
-    <t>{{interviews.date}}</t>
-  </si>
-  <si>
-    <t>{{interviews.speech rating | stars}}</t>
-  </si>
-  <si>
-    <t>{{interviews.tech rating | stars}}</t>
-  </si>
-  <si>
-    <t>{{interviews.decision}}</t>
-  </si>
-  <si>
     <t>Promedio tech</t>
-  </si>
-  <si>
-    <t>Total filas</t>
-  </si>
-  <si>
-    <t>Generado {{@today | date:"dd/MM/yyyy"}}</t>
   </si>
 </sst>
 </file>
@@ -116,13 +65,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
     </font>
     <font>
       <b/>
@@ -166,9 +119,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -510,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -523,129 +477,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1"/>
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="7" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B8"/>
       <c r="G8">
         <f>AVERAGE(G7:G7)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <f>COUNTA(H7:H7)+G8*0</f>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
